--- a/p6_deployment/data/england/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG45"/>
+  <dimension ref="A1:BG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45523.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,128 +779,128 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="O2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.7333333333333329</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AG2" t="n">
         <v>-1</v>
       </c>
-      <c r="P2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.8949999999999998</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.085</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="AH2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>77.95454545454545</v>
+        <v>71.22727272727272</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.54545454545455</v>
+        <v>77.21818181818182</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.630632463511716</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>1.710131649682733</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-1.750895061728386</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-2170909.090909095</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.8393939393939434</v>
-      </c>
+        <v>1.416574074074074</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-1496606.229626353</v>
+        <v>-4.901921991550481</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01515151515153</v>
+        <v>-1.124675669044819</v>
       </c>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-1.594456852916604</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-30074135.80246913</v>
+      </c>
       <c r="AX2" t="n">
-        <v>0.1758826805576206</v>
+        <v>-21386852.84656792</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.002566178518194</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.05421761102101685</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.6666666666666679</v>
-      </c>
+        <v>-5.814135802469153</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0.3818181818181756</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="n">
-        <v>-0.2636363636363639</v>
-      </c>
+        <v>-0.2725935177367069</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-6.836882716049388</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.7213271604938272</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-5.786652515870784</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -908,32 +908,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,128 +960,128 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>6.5</v>
+        <v>-4.333333333333336</v>
       </c>
       <c r="U3" t="n">
-        <v>-4</v>
+        <v>4.333333333333336</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9299999999999998</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.285</v>
+        <v>0.5833333333333335</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>0.5366666666666666</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0.8383333333333336</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.5</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>77.62272727272727</v>
+        <v>78.76801346801348</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.5</v>
+        <v>77.85696969696968</v>
       </c>
       <c r="AN3" t="n">
-        <v>-3.136223368135148</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-1.560371935855681</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.8600168350168076</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-7819999.999999996</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-1.345454545454544</v>
-      </c>
+        <v>-3.155808080808079</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-2737930.412316443</v>
+        <v>-6.906925140326337</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.309090909090855</v>
+        <v>4.734041241776936</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>3.450909090909093</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>-51974579.12457912</v>
+      </c>
       <c r="AX3" t="n">
-        <v>0.290929674900255</v>
+        <v>-29818279.90304367</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1.394916815210919</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.09636257533316339</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.690909090909091</v>
-      </c>
+        <v>-7.229292929292924</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-0.9636363636363683</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="n">
-        <v>-0.01818181818181852</v>
-      </c>
+        <v>-0.6003593821898774</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-4.165824915824913</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.368686868686869</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-3.783660279230858</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1089,32 +1089,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">brentford community stadium
   london </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,128 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>-11.33333333333333</v>
+        <v>-12</v>
       </c>
       <c r="V4" t="n">
-        <v>2.831666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.891666666666667</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>22.66666666666667</v>
+        <v>-0.8949999999999998</v>
       </c>
       <c r="Y4" t="n">
-        <v>-21.66666666666667</v>
+        <v>1.085</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.833333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.166666666666667</v>
+        <v>-3.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF4" t="n">
         <v>-1</v>
       </c>
-      <c r="AE4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>18.33333333333334</v>
-      </c>
       <c r="AG4" t="n">
-        <v>-18.33333333333334</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.333333333333334</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>75.97205387205388</v>
+        <v>77.95454545454545</v>
       </c>
       <c r="AM4" t="n">
-        <v>84.92727272727274</v>
+        <v>76.54545454545455</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1.514809081527346</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>-1.85137343987515</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.9303030303030084</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>47974942.12962963</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6.856481481481467</v>
-      </c>
+        <v>0.262626262626263</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>28676257.99123477</v>
+        <v>0.8422794147322605</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.7152777777777999</v>
+        <v>-3.644003838928569</v>
       </c>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>0.1099439775910405</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>-2567373.737373738</v>
+      </c>
       <c r="AX4" t="n">
-        <v>8.728974173401411</v>
+        <v>590628.4114840962</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.860380898770984</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.4756758205674614</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.576388888888893</v>
-      </c>
+        <v>-0.0929292929292842</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>7.224537037037038</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
-        <v>0.8449074074074074</v>
-      </c>
+        <v>-0.05880993807812152</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.9282828282828177</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.2494949494949499</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.319430534100235</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1270,32 +1270,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45521.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1322,128 +1322,128 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>-4</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.75</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.24</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.1925</v>
+        <v>-4</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.9299999999999998</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3</v>
+        <v>-1.285</v>
       </c>
       <c r="Z5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>-2</v>
-      </c>
       <c r="AB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AC5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-14.75</v>
-      </c>
       <c r="AG5" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>-1.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>77.02146464646464</v>
+        <v>77.62272727272727</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.80000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.780269834859922</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>3.932435117217729</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.4767676767676505</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>2198398.989898991</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.8389898989899081</v>
-      </c>
+        <v>1.720202020202024</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-862436.9560944131</v>
+        <v>-0.23545468179951</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.486262626262658</v>
+        <v>-2.211052703177643</v>
       </c>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>1.574166821572263</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-7140101.010101002</v>
+      </c>
       <c r="AX5" t="n">
-        <v>-0.3981130362137151</v>
+        <v>-5597251.616995063</v>
       </c>
       <c r="AY5" t="n">
-        <v>-3.195366186138841</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.007269238740499784</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.432525252525249</v>
-      </c>
+        <v>-0.686868686868678</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>1.210909090909112</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
-        <v>0.2260606060606059</v>
-      </c>
+        <v>0.003607611248276132</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-1.246464646464659</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.002020202020202255</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-2.078770594755241</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,7 +1451,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,128 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>18.33333333333334</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2999999999999998</v>
+        <v>-18.33333333333334</v>
       </c>
       <c r="V6" t="n">
-        <v>1.316</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3799999999999999</v>
+        <v>-11.33333333333333</v>
       </c>
       <c r="X6" t="n">
-        <v>7.199999999999999</v>
+        <v>2.831666666666667</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.800000000000001</v>
+        <v>-2.891666666666667</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6000000000000001</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.8999999999999999</v>
+        <v>-1</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.5</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.25</v>
+        <v>-3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-2.199999999999999</v>
-      </c>
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-21.66666666666667</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>73.29545454545455</v>
+        <v>75.97205387205388</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.99111111111111</v>
+        <v>84.92727272727274</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.791992086689731</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>0.6395235638114904</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.06126543209876445</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>14857121.21212121</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.874675324675309</v>
-      </c>
+        <v>-1.92546296296296</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>12180272.34625734</v>
+        <v>9.422332167316682</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.000216450216442</v>
+        <v>-1.619370730748443</v>
       </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>1.614797585700945</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>46122029.32098766</v>
+      </c>
       <c r="AX6" t="n">
-        <v>4.436560058806137</v>
+        <v>29354422.66539789</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.942932897796808</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.4727272727272727</v>
-      </c>
+        <v>6.808487654320999</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>4.967316017316037</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="n">
-        <v>0.5060606060606059</v>
-      </c>
+        <v>0.4937788767819729</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.745061728395044</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.7885802469135799</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.836109123075062</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,128 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>-3</v>
       </c>
-      <c r="R7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.4700000000000002</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-2.75</v>
-      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>81.76666666666667</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AM7" t="n">
-        <v>80.13415404040404</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.761489450459663</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>1.850529250983385</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.802918069584734</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.3366666666666731</v>
-      </c>
+        <v>1.552300785634117</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>-131404.7277834453</v>
+        <v>-0.003630135120403111</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.443333333333328</v>
+        <v>8.059273693077529</v>
       </c>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>0.89531110384657</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>1861301.907968573</v>
+      </c>
       <c r="AX7" t="n">
-        <v>1.189468632054457</v>
+        <v>-1243673.984887624</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.6277514713441406</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.1143020154690639</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.533333333333335</v>
-      </c>
+        <v>1.206846240179587</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>0.3599999999999994</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="n">
-        <v>0.1133333333333333</v>
-      </c>
+        <v>-0.0007441557858842707</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-0.9500561167227914</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.2061728395061724</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-3.187342346168066</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1813,32 +1813,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,122 +1865,128 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>-4</v>
+        <v>-2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1925000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.3675</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="X8" t="n">
-        <v>4.25</v>
+        <v>1.316</v>
       </c>
       <c r="Y8" t="n">
-        <v>-9.5</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>-2.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.25</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.3333333333333335</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>-4</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>73.29545454545455</v>
+      </c>
       <c r="AM8" t="n">
-        <v>78.65909090909091</v>
+        <v>72.99111111111111</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.01798654244305453</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>1.187496107898919</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5.630505050505064</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>-46767121.2121212</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-11.44696969696969</v>
-      </c>
+        <v>0.9371950271950311</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>-33372580.22774327</v>
+        <v>2.316979761500221</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.4075757575757279</v>
+        <v>2.569776904680964</v>
       </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>1.849767080745345</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>14679362.08236209</v>
+      </c>
       <c r="AX8" t="n">
-        <v>-10.85770358868186</v>
+        <v>8456518.499563098</v>
       </c>
       <c r="AY8" t="n">
-        <v>-10.96079192546583</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-0.9254227053140098</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.5378787878787854</v>
-      </c>
+        <v>4.997785547785554</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-12.18787878787877</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="n">
-        <v>-1.703030303030303</v>
-      </c>
+        <v>0.3882900432900431</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.616324786324782</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.5293939393939393</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.443425715375852</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1988,32 +1994,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2040,128 +2046,128 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="P9" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>-8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8125</v>
+        <v>-1.75</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.08499999999999996</v>
+        <v>-1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.25</v>
+        <v>-0.0349999999999997</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.5</v>
+        <v>-0.4700000000000002</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AA9" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB9" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-0.75</v>
-      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>78.10954545454544</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AM9" t="n">
-        <v>74.54545454545453</v>
+        <v>80.13415404040404</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.867495183844255</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>0.9373982822216078</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>3.584444444444415</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>16324914.14141415</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.424368686868689</v>
-      </c>
+        <v>0.8288888888888906</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>11235910.75182543</v>
+        <v>0.7075875852733304</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.9743686868686439</v>
+        <v>2.056395486944524</v>
       </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>-3.807347578359405</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>19666.66666666605</v>
+      </c>
       <c r="AX9" t="n">
-        <v>-0.1084503027166051</v>
+        <v>-534417.4824704174</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.024850962123978</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.4951040317312698</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-2.043282828282827</v>
-      </c>
+        <v>-0.1055555555555543</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>2.931060606060598</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="n">
-        <v>0.6678787878787877</v>
-      </c>
+        <v>0.1306318391952392</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.2422222222222388</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.118888888888889</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.007013003037698695</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2169,42 +2175,42 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45518.66666666666</v>
+        <v>45521.35416666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bell j 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6F0lvLNC</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>20242025</v>
@@ -2216,133 +2222,127 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.333333333333333</v>
+        <v>-4</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-2.25</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.066666666666667</v>
+        <v>-4</v>
       </c>
       <c r="X10" t="n">
-        <v>1.666666666666666</v>
+        <v>-0.1925000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>-7.333333333333333</v>
+        <v>-1.3675</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.333333333333333</v>
+        <v>-3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>-2</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>5.666666666666664</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-5.666666666666664</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>72.98888888888888</v>
-      </c>
+      <c r="AH10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
-        <v>69</v>
+        <v>78.65909090909091</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.02683966861602016</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>1.856644212032641</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.7672727272727116</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>6390370.370370369</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.096296296296288</v>
-      </c>
+        <v>0.6181818181818137</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>3713837.719298245</v>
+        <v>-10.55549400194862</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.455555555555605</v>
+        <v>-0.2009810010960678</v>
       </c>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>1.793689083820663</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-44092090.90909091</v>
+      </c>
       <c r="AX10" t="n">
-        <v>6.535148635477583</v>
+        <v>-32198919.6352454</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.317750974658864</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.00164473684210531</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-0.8407407407407419</v>
-      </c>
+        <v>-11.91727272727273</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>5.207407407407402</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="n">
-        <v>0.1666666666666665</v>
-      </c>
+        <v>-0.8132648276701988</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-11.20681818181816</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1.621818181818182</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-11.09582914687613</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2350,42 +2350,42 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45520.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">donohue m 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>20242025</v>
@@ -2397,129 +2397,133 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.08499999999999996</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AI11" t="n">
         <v>3.5</v>
       </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>71.18181818181819</v>
+        <v>77.9919696969697</v>
       </c>
       <c r="AM11" t="n">
-        <v>69.5409090909091</v>
+        <v>74.54545454545453</v>
       </c>
       <c r="AN11" t="n">
-        <v>-4.871307291032338</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
+        <v>-3.82273049426183</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.772474747474746</v>
+      </c>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>1762272.727272727</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.716666666666669</v>
-      </c>
+        <v>-2.187542087542088</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>1835970.306600901</v>
+        <v>0.3442508678921712</v>
       </c>
       <c r="AT11" t="n">
-        <v>-2.096969696969666</v>
+        <v>2.684438527277422</v>
       </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-0.7349977672228327</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>16866637.20538721</v>
+      </c>
       <c r="AX11" t="n">
-        <v>3.686903747006042</v>
+        <v>12046064.33408343</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.701822758088753</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.01249999999999996</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-3.16363636363636</v>
-      </c>
+        <v>2.726262626262638</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>1.980303030303034</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="n">
-        <v>0.09090909090909105</v>
-      </c>
+        <v>0.5558858743321657</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.328535353535358</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.6883838383838383</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.367332947671812</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2527,27 +2531,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2574,57 +2583,127 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.3266666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-7.333333333333333</v>
+      </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
+        <v>72.98888888888888</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.537110809082559</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.31852617079889</v>
+      </c>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-1.11623048668503</v>
+      </c>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>7.334945108426126</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.362754095319872</v>
+      </c>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>6015646.235078054</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3510151.26442937</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.410445362718065</v>
+      </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>0.06099221985444903</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.632380624426091</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.1529958677685948</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.212224376930266</v>
+      </c>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2633,27 +2712,27 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45517.66666666666</v>
+        <v>45518.65625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IgO7K1ZA</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2680,22 +2759,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2718,7 +2789,7 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>76.57205387205387</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
@@ -2747,27 +2818,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>45518.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2792,57 +2868,129 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>69.5409090909091</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.083286126447355</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-3.375252525252478</v>
+      </c>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>-2.49267676767677</v>
+      </c>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>3.658565308168363</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-4.083728128932705</v>
+      </c>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>1897077.02020202</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1286850.884526516</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.596212121212119</v>
+      </c>
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>0.005927050771999509</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.459595959595973</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.09393939393939421</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.174513595695927</v>
+      </c>
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="n">
         <v>0</v>
@@ -2851,27 +2999,27 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2896,12 +3044,24 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2923,7 +3083,9 @@
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>76.57205387205387</v>
+      </c>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
@@ -2951,32 +3113,27 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3001,12 +3158,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>-2</v>
       </c>
@@ -3036,10 +3193,10 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AL16" t="n">
+        <v>69.13636363636363</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
@@ -3066,32 +3223,27 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3116,21 +3268,13 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q17" t="n">
         <v>-1</v>
@@ -3141,105 +3285,45 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>21</v>
-      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>74</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>69</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-0.3179805865900676</v>
-      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="n">
-        <v>-913171.2962962962</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-4.75833333333334</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>-113208.6218672572</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.131481481481472</v>
-      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="n">
-        <v>0.8968506802670184</v>
-      </c>
+      <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="n">
-        <v>0.6488685481820511</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>-0.3063794040372159</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.047222222222217</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0.9592592592592553</v>
-      </c>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
+      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3247,27 +3331,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3294,61 +3383,127 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1</v>
+      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-21</v>
+      </c>
+      <c r="U18" t="n">
+        <v>21</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9</v>
+      </c>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>69.13636363636363</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.018441460376287</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2.117245370370341</v>
+      </c>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>4.656327160493827</v>
+      </c>
       <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>0.3003679171335136</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.5588051963200087</v>
+      </c>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>-1287210.648148148</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-109708.5345255611</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.2523148148148096</v>
+      </c>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-5.889969135802474</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0.4068603831073148</v>
+      </c>
       <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3357,7 +3512,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3366,18 +3521,18 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3405,17 +3560,13 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -3465,27 +3616,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3511,19 +3667,19 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>0</v>
       </c>
@@ -3546,7 +3702,9 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
@@ -3787,7 +3945,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -3796,18 +3954,18 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3834,18 +3992,10 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -3895,7 +4045,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -3904,18 +4054,18 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3940,23 +4090,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3979,9 +4125,7 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
@@ -4113,7 +4257,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4122,18 +4266,18 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4160,18 +4304,22 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1</v>
+      </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
@@ -4194,7 +4342,7 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>70.70833333333333</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
@@ -4223,7 +4371,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -4232,18 +4380,18 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4270,10 +4418,18 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
@@ -4323,32 +4479,27 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,11 +4525,7 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -4405,9 +4552,7 @@
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
@@ -4434,7 +4579,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -4443,18 +4588,18 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4479,10 +4624,18 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
@@ -4506,7 +4659,9 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>70.70833333333333</v>
+      </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
@@ -4534,27 +4689,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4579,53 +4739,129 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>21</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-21</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>-24</v>
+      </c>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.481839318662072</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>-1.653888888888872</v>
+      </c>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
+      <c r="AQ30" t="n">
+        <v>-0.617986111111108</v>
+      </c>
       <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
+      <c r="AS30" t="n">
+        <v>-2.218100666103766</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.2448807569279836</v>
+      </c>
       <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AW30" t="n">
+        <v>-2184951.388888889</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>-1374683.396464646</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-2.831736111111098</v>
+      </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
-      <c r="BD30" t="inlineStr"/>
-      <c r="BE30" t="inlineStr"/>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>-2.584305555555559</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>-2.872966736136249</v>
+      </c>
       <c r="BF30" t="inlineStr"/>
       <c r="BG30" t="n">
         <v>0</v>
@@ -4634,27 +4870,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4680,7 +4921,11 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -4707,7 +4952,9 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
@@ -4734,32 +4981,27 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4784,130 +5026,54 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>4</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
         <v>0</v>
       </c>
-      <c r="T32" t="n">
-        <v>4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>-6</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W32" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="X32" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>-24</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>-21</v>
-      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>70.18181818181819</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>-1.610778081567503</v>
-      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="n">
-        <v>-2171296.296296297</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>-2.606111111111105</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>-1147986.386420596</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>-0.975555555555502</v>
-      </c>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="n">
-        <v>1.610061517429937</v>
-      </c>
+      <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="n">
-        <v>-1.164470266575535</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>-2.090940419229881</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>-0.7666666666666693</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>-2.892777777777781</v>
-      </c>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
       <c r="BE32" t="inlineStr"/>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
+      <c r="BF32" t="inlineStr"/>
       <c r="BG32" t="n">
         <v>0</v>
       </c>
@@ -4915,7 +5081,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -4924,18 +5090,18 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5015,32 +5181,27 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5065,12 +5226,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -5096,10 +5257,10 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="n">
-        <v>71.77777777777777</v>
-      </c>
+      <c r="AL34" t="n">
+        <v>69.33522727272728</v>
+      </c>
+      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
@@ -5226,32 +5387,27 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,17 +5433,9 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>2</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
@@ -5312,9 +5460,7 @@
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
@@ -5341,7 +5487,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -5350,18 +5496,18 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5389,10 +5535,10 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -5445,27 +5591,32 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5490,12 +5641,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -5521,10 +5672,10 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="n">
-        <v>69.33522727272728</v>
-      </c>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
@@ -5551,7 +5702,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5560,18 +5711,18 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5596,13 +5747,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -5627,7 +5782,9 @@
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>71.47727272727272</v>
+      </c>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
@@ -5655,27 +5812,32 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5701,12 +5863,16 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -5732,7 +5898,9 @@
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
+      <c r="AM40" t="n">
+        <v>67.40000000000001</v>
+      </c>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
@@ -5759,7 +5927,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -5768,18 +5936,18 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5804,17 +5972,13 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P41" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -5839,9 +6003,7 @@
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
@@ -5869,32 +6031,27 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5920,13 +6077,13 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
@@ -5951,9 +6108,7 @@
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
@@ -5980,32 +6135,27 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6031,11 +6181,7 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -6062,9 +6208,7 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="n">
-        <v>76</v>
-      </c>
+      <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
@@ -6091,27 +6235,32 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6137,13 +6286,13 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>-1</v>
-      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
@@ -6168,7 +6317,9 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+      <c r="AM44" t="n">
+        <v>76</v>
+      </c>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
@@ -6195,45 +6346,40 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45514.45833333334</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
+          <t xml:space="preserve">brisbane road
   london </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>48</v>
       </c>
       <c r="H45" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6242,134 +6388,354 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>fa community shield</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="P45" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>-4</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="n">
-        <v>2</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.1174999999999999</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.5950000000000002</v>
-      </c>
-      <c r="X45" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>7</v>
-      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>76.15625</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>77.36540404040404</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>5.976728453238991</v>
-      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="n">
-        <v>-46160858.58585859</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>-3.410858585858577</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>-26308142.17514245</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>2.386868686868638</v>
-      </c>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
       <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="n">
-        <v>-0.4983721947276933</v>
-      </c>
+      <c r="AV45" t="inlineStr"/>
       <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="n">
-        <v>-5.795527952617149</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>-3.781344512442644</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>-0.5157635798060989</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>-2.023737373737372</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>-5.946212121212142</v>
-      </c>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="inlineStr"/>
       <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="n">
-        <v>-1.022348484848485</v>
-      </c>
+      <c r="BF45" t="inlineStr"/>
       <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>dUzTIwSF</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>48</v>
+      </c>
+      <c r="H46" t="n">
+        <v>484</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wembley stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" t="n">
+        <v>482</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>fa community shield</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="U47" t="n">
+        <v>7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.1174999999999999</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.5950000000000002</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>76.15625</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>77.36540404040404</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>-0.3707263230281157</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2.906565656565647</v>
+      </c>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="n">
+        <v>-1.729208754208756</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="n">
+        <v>-4.997674767096129</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>5.760937278951985</v>
+      </c>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="n">
+        <v>-43387504.2087542</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>-25716382.34990418</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>-5.511616161616161</v>
+      </c>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="n">
+        <v>-0.4099647291942687</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>-3.101262626262624</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>-0.9106060606060611</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>-3.458909711227491</v>
+      </c>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/england/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_constructed.xlsx
@@ -500,24 +500,24 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -525,84 +525,84 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -791,28 +791,28 @@
         <v>-3</v>
       </c>
       <c r="P2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-10.5</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="U2" t="n">
-        <v>10.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="W2" t="n">
-        <v>-5.333333333333333</v>
+        <v>-7.666666666666666</v>
       </c>
       <c r="X2" t="n">
         <v>-0.7333333333333329</v>
@@ -821,16 +821,16 @@
         <v>-0.8333333333333335</v>
       </c>
       <c r="Z2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.1666666666666661</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>-5.333333333333334</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.666666666666667</v>
       </c>
       <c r="AD2" t="n">
         <v>0.5</v>
@@ -839,16 +839,16 @@
         <v>-0.5</v>
       </c>
       <c r="AF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.8333333333333333</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>-1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-7.666666666666666</v>
       </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -858,49 +858,49 @@
       <c r="AM2" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AN2" t="n">
-        <v>1.710131649682733</v>
-      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-1.750895061728386</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-5.786111111111126</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-29846130.95238096</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>1.416574074074074</v>
+        <v>-6.928968253968279</v>
       </c>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-4.901921991550481</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-1.124675669044819</v>
+        <v>-0.6529583972743467</v>
       </c>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-0.6529761904761904</v>
+      </c>
       <c r="AW2" t="n">
-        <v>-30074135.80246913</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-21386852.84656792</v>
-      </c>
+        <v>1.610714285714284</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-5.814135802469153</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>-0.2725935177367069</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-6.836882716049388</v>
-      </c>
+        <v>1.697725122744469</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-2.036111111111097</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.2652031356801094</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-0.7213271604938272</v>
+        <v>-4.617364768874054</v>
       </c>
       <c r="BE2" t="n">
-        <v>-5.786652515870784</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>-5.53524554758107</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-20828499.91459402</v>
+      </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -972,28 +972,28 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-4.333333333333336</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>4.333333333333336</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>2.083333333333334</v>
+        <v>6.75</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5833333333333335</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
         <v>0.5366666666666666</v>
@@ -1002,16 +1002,16 @@
         <v>0.8383333333333336</v>
       </c>
       <c r="Z3" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="AB3" t="n">
         <v>3.166666666666666</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>1.416666666666666</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.666666666666667</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3999999999999999</v>
@@ -1020,16 +1020,16 @@
         <v>-0.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="AG3" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>10</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -1037,51 +1037,51 @@
         <v>78.76801346801348</v>
       </c>
       <c r="AM3" t="n">
-        <v>77.85696969696968</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-1.560371935855681</v>
-      </c>
+        <v>77.85375573921029</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>0.8600168350168076</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-7.186501377410465</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-51413177.2268136</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>-3.155808080808079</v>
+        <v>-4.217263544536266</v>
       </c>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>-6.906925140326337</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>4.734041241776936</v>
+        <v>4.662498772541994</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>-1.347658402203856</v>
+      </c>
       <c r="AW3" t="n">
-        <v>-51974579.12457912</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-29818279.90304367</v>
-      </c>
+        <v>-3.051790633608814</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>-7.229292929292924</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>-0.6003593821898774</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-4.165824915824913</v>
-      </c>
+        <v>-1.691146771888398</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.020018365472879</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.6495899142606152</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-1.368686868686869</v>
+        <v>-6.978295722220025</v>
       </c>
       <c r="BE3" t="n">
-        <v>-3.783660279230858</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>-3.821670648389343</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-30582204.89040975</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1156,25 +1156,25 @@
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>-5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>-0.8949999999999998</v>
@@ -1183,16 +1183,16 @@
         <v>1.085</v>
       </c>
       <c r="Z4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AB4" t="n">
         <v>-4.5</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>-3.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>-1.5</v>
@@ -1201,16 +1201,16 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-1</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1220,49 +1220,49 @@
       <c r="AM4" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AN4" t="n">
-        <v>-1.85137343987515</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>0.9303030303030084</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>-0.02499999999999147</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-2840227.272727277</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>0.262626262626263</v>
+        <v>-1.015909090909076</v>
       </c>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>0.8422794147322605</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-3.644003838928569</v>
+        <v>-3.412103922423285</v>
       </c>
       <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-0.2500000000000004</v>
+      </c>
       <c r="AW4" t="n">
-        <v>-2567373.737373738</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>590628.4114840962</v>
-      </c>
+        <v>0.4215909090909093</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>-0.0929292929292842</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>-0.05880993807812152</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.9282828282828177</v>
-      </c>
+        <v>-1.758528781459191</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.8818181818181756</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.0591532846929772</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>-0.2494949494949499</v>
+        <v>0.5584070336754223</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.319430534100235</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+        <v>1.213244601807162</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-373016.4704373358</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1334,28 +1334,28 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>0.9299999999999998</v>
@@ -1364,16 +1364,16 @@
         <v>-1.285</v>
       </c>
       <c r="Z5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1</v>
       </c>
       <c r="AD5" t="n">
         <v>2</v>
@@ -1382,16 +1382,16 @@
         <v>-2.5</v>
       </c>
       <c r="AF5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>-1.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1401,49 +1401,49 @@
       <c r="AM5" t="n">
         <v>76.5</v>
       </c>
-      <c r="AN5" t="n">
-        <v>3.932435117217729</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>0.4767676767676505</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>-0.5788961038960849</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-6566688.311688308</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>1.720202020202024</v>
+        <v>-1.115584415584408</v>
       </c>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-0.23545468179951</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-2.211052703177643</v>
+        <v>-2.344286824578319</v>
       </c>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>0.03051948051948061</v>
+      </c>
       <c r="AW5" t="n">
-        <v>-7140101.010101002</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-5597251.616995063</v>
-      </c>
+        <v>1.751623376623378</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>-0.686868686868678</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>0.003607611248276132</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1.246464646464659</v>
-      </c>
+        <v>3.723382610620007</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.532467532467507</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.01246849118435223</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>-0.002020202020202255</v>
+        <v>-0.1528413069773364</v>
       </c>
       <c r="BE5" t="n">
-        <v>-2.078770594755241</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>-1.910130074757177</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-5104078.211303459</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1515,28 +1515,28 @@
         <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>18.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-18.33333333333334</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>-11.33333333333333</v>
+        <v>-21.66666666666667</v>
       </c>
       <c r="X6" t="n">
         <v>2.831666666666667</v>
@@ -1545,16 +1545,16 @@
         <v>-2.891666666666667</v>
       </c>
       <c r="Z6" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="AB6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>2.333333333333334</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1</v>
       </c>
       <c r="AD6" t="n">
         <v>3</v>
@@ -1563,16 +1563,16 @@
         <v>-3</v>
       </c>
       <c r="AF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>-3.166666666666667</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-21.66666666666667</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1582,49 +1582,49 @@
       <c r="AM6" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AN6" t="n">
-        <v>0.6395235638114904</v>
-      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>0.06126543209876445</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>6.823302469135797</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>45962553.04783951</v>
+      </c>
       <c r="AQ6" t="n">
-        <v>-1.92546296296296</v>
+        <v>6.690779320987659</v>
       </c>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>9.422332167316682</v>
-      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>-1.619370730748443</v>
+        <v>-1.181552868356249</v>
       </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0.7966820987654317</v>
+      </c>
       <c r="AW6" t="n">
-        <v>46122029.32098766</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>29354422.66539789</v>
-      </c>
+        <v>-1.871527777777775</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>6.808487654320999</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>0.4937788767819729</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.745061728395044</v>
-      </c>
+        <v>0.359199190042844</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.1163194444444287</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.4806652884439262</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>0.7885802469135799</v>
+        <v>9.138795685738401</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.836109123075062</v>
-      </c>
-      <c r="BF6" t="inlineStr"/>
+        <v>5.931281691304903</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>29274081.18949334</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,128 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-14.75</v>
+        <v>-0.25</v>
       </c>
       <c r="U7" t="n">
-        <v>14.75</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0349999999999997</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC7" t="n">
         <v>-2.75</v>
       </c>
-      <c r="X7" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-1.1925</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AG7" t="n">
         <v>-1</v>
       </c>
-      <c r="AD7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-2</v>
-      </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>77.02146464646464</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AM7" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.850529250983385</v>
-      </c>
+        <v>80.13415404040404</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>1.802918069584734</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>-0.03749999999999432</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-112321.4285714291</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>1.552300785634117</v>
+        <v>-0.2910714285714278</v>
       </c>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>-0.003630135120403111</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>8.059273693077529</v>
+        <v>2.362852243863756</v>
       </c>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0.1089285714285715</v>
+      </c>
       <c r="AW7" t="n">
-        <v>1861301.907968573</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-1243673.984887624</v>
-      </c>
+        <v>0.9857142857142875</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>1.206846240179587</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>-0.0007441557858842707</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-0.9500561167227914</v>
-      </c>
+        <v>0.9000830395087078</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.742857142857105</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.1161873589842288</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>0.2061728395061724</v>
+        <v>0.9510967786844304</v>
       </c>
       <c r="BE7" t="n">
-        <v>-3.187342346168066</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+        <v>0.3619543532862792</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-238945.7190112025</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1813,7 +1813,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1821,24 +1821,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,128 +1865,128 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.3799999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-2.800000000000001</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.7000000000000002</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.6000000000000001</v>
-      </c>
       <c r="AE8" t="n">
-        <v>-0.8999999999999999</v>
+        <v>-2</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.800000000000001</v>
+        <v>-2</v>
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>73.29545454545455</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AM8" t="n">
-        <v>72.99111111111111</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.187496107898919</v>
-      </c>
+        <v>75.80000000000001</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>5.630505050505064</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>1.214520202020211</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1834589.646464648</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>0.9371950271950311</v>
+        <v>-1.000631313131322</v>
       </c>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>2.316979761500221</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>2.569776904680964</v>
+        <v>8.367477054386455</v>
       </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>0.213762626262626</v>
+      </c>
       <c r="AW8" t="n">
-        <v>14679362.08236209</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8456518.499563098</v>
-      </c>
+        <v>1.680429292929293</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>4.997785547785554</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>0.3882900432900431</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.616324786324782</v>
-      </c>
+        <v>1.436444162587492</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.566919191919197</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.04747189620826719</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>0.5293939393939393</v>
+        <v>-0.2379628116184165</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.443425715375852</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+        <v>-3.104791532682242</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-1201358.571683187</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1994,7 +1994,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2002,24 +2002,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2046,128 +2046,128 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.75</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-1</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0349999999999997</v>
+        <v>1.316</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.4700000000000002</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.75</v>
+        <v>-2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.25</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.75</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.75</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.75</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>3.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>81.76666666666667</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="AM9" t="n">
-        <v>80.13415404040404</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.9373982822216078</v>
-      </c>
+        <v>72.99111111111111</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>3.584444444444415</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>4.902169421487613</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14692283.05785124</v>
+      </c>
       <c r="AQ9" t="n">
-        <v>0.8288888888888906</v>
+        <v>4.699896694214871</v>
       </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>0.7075875852733304</v>
-      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>2.056395486944524</v>
+        <v>2.517704458265484</v>
       </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>0.5102272727272728</v>
+      </c>
       <c r="AW9" t="n">
-        <v>19666.66666666605</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-534417.4824704174</v>
-      </c>
+        <v>0.7660123966942081</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>-0.1055555555555543</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>0.1306318391952392</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.2422222222222388</v>
-      </c>
+        <v>1.409744653790366</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.375206611570235</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.4238095238095236</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>0.118888888888889</v>
+        <v>3.202640962511481</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.007013003037698695</v>
-      </c>
-      <c r="BF9" t="inlineStr"/>
+        <v>2.96223784474266</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>10053627.24598238</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2238,25 +2238,25 @@
       <c r="O10" t="n">
         <v>-3</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
         <v>-3</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-4</v>
+        <v>0.25</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.25</v>
+        <v>4.25</v>
       </c>
       <c r="W10" t="n">
-        <v>-4</v>
+        <v>-9.5</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1925000000000001</v>
@@ -2265,16 +2265,16 @@
         <v>-1.3675</v>
       </c>
       <c r="Z10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
         <v>-3.25</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
         <v>1.75</v>
@@ -2283,16 +2283,16 @@
         <v>-1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>-2.25</v>
       </c>
       <c r="AG10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>-2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-9.5</v>
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
@@ -2300,49 +2300,49 @@
       <c r="AM10" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AN10" t="n">
-        <v>1.856644212032641</v>
-      </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>-0.7672727272727116</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
+        <v>-12.20606060606062</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-45110909.09090909</v>
+      </c>
       <c r="AQ10" t="n">
-        <v>0.6181818181818137</v>
+        <v>-11.28787878787877</v>
       </c>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>-10.55549400194862</v>
-      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>-0.2009810010960678</v>
+        <v>-0.06185875316307943</v>
       </c>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-1.65050505050505</v>
+      </c>
       <c r="AW10" t="n">
-        <v>-44092090.90909091</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-32198919.6352454</v>
-      </c>
+        <v>0.4595959595959549</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="n">
-        <v>-11.91727272727273</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
-        <v>-0.8132648276701988</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-11.20681818181816</v>
-      </c>
+        <v>1.938006096158269</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.6909090909090878</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.8513400046008743</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-1.621818181818182</v>
+        <v>-10.60447435012652</v>
       </c>
       <c r="BE10" t="n">
-        <v>-11.09582914687613</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+        <v>-11.21757821486082</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-32647976.76558546</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2414,28 +2414,28 @@
         <v>22</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="n">
-        <v>2.75</v>
+        <v>5.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="X11" t="n">
         <v>0.8125</v>
@@ -2444,16 +2444,16 @@
         <v>-0.08499999999999996</v>
       </c>
       <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>-4.25</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>-0.75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
         <v>-0.3999999999999999</v>
@@ -2462,68 +2462,68 @@
         <v>0.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.5</v>
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>77.9919696969697</v>
+        <v>77.97987603305785</v>
       </c>
       <c r="AM11" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AN11" t="n">
-        <v>-3.82273049426183</v>
-      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>0.772474747474746</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
+        <v>2.722746950019683</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17019983.60225633</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>-2.187542087542088</v>
+        <v>5.466745375836283</v>
       </c>
       <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>0.3442508678921712</v>
-      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>2.684438527277422</v>
+        <v>2.544944017851492</v>
       </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>0.6762691853600942</v>
+      </c>
       <c r="AW11" t="n">
-        <v>16866637.20538721</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>12046064.33408343</v>
-      </c>
+        <v>-2.333989243080151</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="n">
-        <v>2.726262626262638</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>0.5558858743321657</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.328535353535358</v>
-      </c>
+        <v>-3.654831907610326</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.7954742227468898</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.5276486675638035</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>0.6883838383838383</v>
+        <v>0.02235611336402599</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.367332947671812</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+        <v>5.024274162893079</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>10984469.04336654</v>
+      </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2595,28 +2595,28 @@
         <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>5.666666666666664</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.666666666666664</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.333333333333333</v>
+        <v>-7.333333333333333</v>
       </c>
       <c r="X12" t="n">
         <v>-0.3266666666666667</v>
@@ -2625,16 +2625,16 @@
         <v>-1.066666666666667</v>
       </c>
       <c r="Z12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="AB12" t="n">
         <v>6.666666666666668</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>7</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
       </c>
       <c r="AD12" t="n">
         <v>-2</v>
@@ -2643,16 +2643,16 @@
         <v>2</v>
       </c>
       <c r="AF12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH12" t="n">
         <v>-2.333333333333333</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.666666666666666</v>
-      </c>
       <c r="AI12" t="n">
-        <v>-7.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -2662,49 +2662,49 @@
       <c r="AM12" t="n">
         <v>69</v>
       </c>
-      <c r="AN12" t="n">
-        <v>2.537110809082559</v>
-      </c>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>2.31852617079889</v>
-      </c>
-      <c r="AP12" t="inlineStr"/>
+        <v>4.648877665544319</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6137873.176206509</v>
+      </c>
       <c r="AQ12" t="n">
-        <v>-1.11623048668503</v>
+        <v>4.746520763187448</v>
       </c>
       <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="n">
-        <v>7.334945108426126</v>
-      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1.362754095319872</v>
+        <v>0.8657106619825754</v>
       </c>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>0.1550505050505051</v>
+      </c>
       <c r="AW12" t="n">
-        <v>6015646.235078054</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3510151.26442937</v>
-      </c>
+        <v>-1.061503928170595</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="n">
-        <v>4.410445362718065</v>
-      </c>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
-        <v>0.06099221985444903</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.632380624426091</v>
-      </c>
+        <v>2.571972157433972</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.392087542087609</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.04603727455894635</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="n">
-        <v>0.1529958677685948</v>
+        <v>7.331146766698879</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.212224376930266</v>
-      </c>
-      <c r="BF12" t="inlineStr"/>
+        <v>3.016572387689507</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3577584.255148304</v>
+      </c>
       <c r="BG12" t="n">
         <v>0</v>
       </c>
@@ -2882,25 +2882,25 @@
         <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>21.5</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-21.5</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
         <v>8</v>
@@ -2912,16 +2912,16 @@
         <v>0.665</v>
       </c>
       <c r="Z14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="AB14" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>7.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-1</v>
       </c>
       <c r="AD14" t="n">
         <v>-2</v>
@@ -2930,16 +2930,16 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>8</v>
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
@@ -2949,49 +2949,49 @@
       <c r="AM14" t="n">
         <v>69.5409090909091</v>
       </c>
-      <c r="AN14" t="n">
-        <v>-0.083286126447355</v>
-      </c>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>-3.375252525252478</v>
-      </c>
-      <c r="AP14" t="inlineStr"/>
+        <v>2.123376623376615</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1776341.991341992</v>
+      </c>
       <c r="AQ14" t="n">
-        <v>-2.49267676767677</v>
+        <v>4.493073593073603</v>
       </c>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="n">
-        <v>3.658565308168363</v>
-      </c>
+      <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>-4.083728128932705</v>
+        <v>-4.192364047068082</v>
       </c>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>0.09220779220779241</v>
+      </c>
       <c r="AW14" t="n">
-        <v>1897077.02020202</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1286850.884526516</v>
-      </c>
+        <v>-2.962770562770565</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="n">
-        <v>2.596212121212119</v>
-      </c>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="n">
-        <v>0.005927050771999509</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.459595959595973</v>
-      </c>
+        <v>0.0640253202730392</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-3.160173160173173</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.01481295416717421</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="n">
-        <v>0.09393939393939421</v>
+        <v>4.043052003410054</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.174513595695927</v>
-      </c>
-      <c r="BF14" t="inlineStr"/>
+        <v>4.433221114532756</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1651013.664523781</v>
+      </c>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3050,18 +3050,10 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -3113,27 +3105,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3158,19 +3155,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
       <c r="O16" t="n">
         <v>-2</v>
       </c>
-      <c r="P16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
         <v>0</v>
@@ -3193,10 +3190,10 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="n">
-        <v>69.13636363636363</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
@@ -3223,7 +3220,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3232,18 +3229,18 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3268,20 +3265,20 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>-2</v>
       </c>
-      <c r="P17" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
         <v>-1</v>
       </c>
-      <c r="R17" t="n">
-        <v>-1</v>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -3303,7 +3300,9 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>69.13636363636363</v>
+      </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
@@ -3331,32 +3330,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3381,129 +3375,53 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-1</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="n">
-        <v>-21</v>
-      </c>
-      <c r="U18" t="n">
-        <v>21</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>8</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9</v>
-      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="n">
-        <v>74</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>69</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.018441460376287</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2.117245370370341</v>
-      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="n">
-        <v>4.656327160493827</v>
-      </c>
+      <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="n">
-        <v>0.3003679171335136</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.5588051963200087</v>
-      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="n">
-        <v>-1287210.648148148</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-109708.5345255611</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0.2523148148148096</v>
-      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>-5.889969135802474</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>-0.4068603831073148</v>
-      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3512,7 +3430,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3521,18 +3439,18 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3559,12 +3477,8 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
@@ -3616,32 +3530,27 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3667,18 +3576,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>0</v>
@@ -3702,9 +3607,7 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
@@ -3731,7 +3634,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3740,18 +3643,18 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3776,15 +3679,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>0</v>
@@ -3807,7 +3714,9 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>69.2</v>
+      </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
@@ -3835,7 +3744,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -3844,18 +3753,18 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3882,18 +3791,22 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1</v>
+      </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
@@ -3916,7 +3829,7 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>69.2</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
@@ -3945,7 +3858,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -3954,18 +3867,18 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4045,7 +3958,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -4054,18 +3967,18 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4090,20 +4003,20 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -4125,7 +4038,9 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AL24" t="n">
+        <v>70.70833333333333</v>
+      </c>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
@@ -4153,7 +4068,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -4162,18 +4077,18 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4200,12 +4115,8 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
@@ -4257,7 +4168,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4266,18 +4177,18 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">dw stadium
+  wigan </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4302,24 +4213,16 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
         <v>0</v>
       </c>
@@ -4341,9 +4244,7 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
@@ -4371,7 +4272,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -4380,18 +4281,18 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4418,18 +4319,10 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>0</v>
       </c>
@@ -4479,7 +4372,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -4488,18 +4381,18 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4526,8 +4419,12 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
@@ -4579,27 +4476,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4626,62 +4528,128 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
       <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
+      <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2</v>
+      </c>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>70.70833333333333</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>69</v>
+      </c>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
+      <c r="AO29" t="n">
+        <v>0.3376984126984013</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>-1281253.306878306</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>-5.914153439153438</v>
+      </c>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0.2953982603720817</v>
+      </c>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.621296296296293</v>
+      </c>
       <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
+      <c r="AY29" t="n">
+        <v>1.216519796764572</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.906944444444434</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
-      <c r="BF29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>0.4217652273900256</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>-0.5411850373547225</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>-130365.5393059938</v>
+      </c>
       <c r="BG29" t="n">
         <v>0</v>
       </c>
@@ -4689,32 +4657,27 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4739,129 +4702,53 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30" t="n">
-        <v>21</v>
-      </c>
-      <c r="U30" t="n">
-        <v>-21</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>-24</v>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>70.18181818181819</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.481839318662072</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>-1.653888888888872</v>
-      </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="n">
-        <v>-0.617986111111108</v>
-      </c>
+      <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="n">
-        <v>-2.218100666103766</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.2448807569279836</v>
-      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr"/>
       <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="n">
-        <v>-2184951.388888889</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>-1374683.396464646</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>-2.831736111111098</v>
-      </c>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>-2.584305555555559</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>-2.872966736136249</v>
-      </c>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="inlineStr"/>
       <c r="BG30" t="n">
         <v>0</v>
@@ -4870,32 +4757,27 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4921,11 +4803,7 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -4952,9 +4830,7 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
@@ -4981,7 +4857,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -4990,18 +4866,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5081,7 +4957,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -5090,18 +4966,18 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5181,7 +5057,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -5190,18 +5066,18 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5226,11 +5102,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -5257,9 +5129,7 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="n">
-        <v>69.33522727272728</v>
-      </c>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
@@ -5287,7 +5157,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5296,18 +5166,18 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5332,7 +5202,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -5359,7 +5233,9 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AL35" t="n">
+        <v>69.33522727272728</v>
+      </c>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
@@ -5387,27 +5263,32 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5432,54 +5313,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-24</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>70.18181818181819</v>
+      </c>
       <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>-2.816666666666649</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>-2234641.203703703</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>-2.82534722222222</v>
+      </c>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>-0.2023692810457476</v>
+      </c>
       <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>-0.5010416666666657</v>
+      </c>
       <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
+      <c r="AY36" t="n">
+        <v>1.301905073233439</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>-1.420370370370335</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
+      <c r="BD36" t="n">
+        <v>-2.202103660443441</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>-2.49301163447835</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>-1269591.292981506</v>
+      </c>
       <c r="BG36" t="n">
         <v>0</v>
       </c>
@@ -5487,27 +5444,32 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5533,13 +5495,13 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
@@ -5564,7 +5526,9 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AM37" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
@@ -5591,7 +5555,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -5599,24 +5563,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5644,12 +5608,16 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
         <v>0</v>
@@ -5674,7 +5642,7 @@
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="n">
-        <v>71.77777777777777</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
@@ -5702,7 +5670,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5711,18 +5679,18 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5747,19 +5715,15 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
         <v>-1</v>
       </c>
-      <c r="P39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>0</v>
@@ -5782,9 +5746,7 @@
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
@@ -5812,32 +5774,27 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5862,18 +5819,14 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2</v>
-      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
@@ -5897,10 +5850,10 @@
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AL40" t="n">
+        <v>71.47727272727272</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="inlineStr"/>
@@ -5927,27 +5880,32 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5973,13 +5931,13 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-2</v>
-      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
@@ -6004,7 +5962,9 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
+      <c r="AM41" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
@@ -6031,7 +5991,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6040,18 +6000,18 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6078,12 +6038,8 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
@@ -6135,7 +6091,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -6144,18 +6100,18 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6235,7 +6191,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -6243,24 +6199,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6288,7 +6244,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -6318,7 +6274,7 @@
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
@@ -6346,27 +6302,32 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6392,13 +6353,13 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>-1</v>
-      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
@@ -6423,7 +6384,9 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AM45" t="n">
+        <v>76</v>
+      </c>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
@@ -6450,32 +6413,27 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">brisbane road
+  london </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6501,11 +6459,7 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -6532,9 +6486,7 @@
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
       <c r="AP46" t="inlineStr"/>
@@ -6625,28 +6577,28 @@
         <v>6</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="Q47" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="W47" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="X47" t="n">
         <v>0.1174999999999999</v>
@@ -6655,16 +6607,16 @@
         <v>0.5950000000000002</v>
       </c>
       <c r="Z47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB47" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AC47" t="n">
         <v>-2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.5</v>
       </c>
       <c r="AD47" t="n">
         <v>-1.25</v>
@@ -6673,16 +6625,16 @@
         <v>1</v>
       </c>
       <c r="AF47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH47" t="n">
         <v>-1</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>6.5</v>
       </c>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
@@ -6692,49 +6644,49 @@
       <c r="AM47" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AN47" t="n">
-        <v>-0.3707263230281157</v>
-      </c>
+      <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="n">
-        <v>2.906565656565647</v>
-      </c>
-      <c r="AP47" t="inlineStr"/>
+        <v>-5.467217630854009</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>-42477277.31864096</v>
+      </c>
       <c r="AQ47" t="n">
-        <v>-1.729208754208756</v>
+        <v>-3.063360881542692</v>
       </c>
       <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="n">
-        <v>-4.997674767096129</v>
-      </c>
+      <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
-        <v>5.760937278951985</v>
+        <v>5.571349283515019</v>
       </c>
       <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
+      <c r="AV47" t="n">
+        <v>-0.8917355371900828</v>
+      </c>
       <c r="AW47" t="n">
-        <v>-43387504.2087542</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>-25716382.34990418</v>
-      </c>
+        <v>-1.708723599632687</v>
+      </c>
+      <c r="AX47" t="inlineStr"/>
       <c r="AY47" t="n">
-        <v>-5.511616161616161</v>
-      </c>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="n">
-        <v>-0.4099647291942687</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>-3.101262626262624</v>
-      </c>
+        <v>-0.6278392923824185</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>2.907988980716226</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>-0.4772401918007592</v>
+      </c>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
       <c r="BD47" t="n">
-        <v>-0.9106060606060611</v>
+        <v>-5.534005271769757</v>
       </c>
       <c r="BE47" t="n">
-        <v>-3.458909711227491</v>
-      </c>
-      <c r="BF47" t="inlineStr"/>
+        <v>-3.686012020091297</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>-27542234.39953895</v>
+      </c>
       <c r="BG47" t="n">
         <v>1</v>
       </c>

--- a/p6_deployment/data/england/data_preparation/df_constructed.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -803,103 +803,103 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AC2" t="n">
         <v>-1.666666666666667</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AD2" t="n">
+        <v>-0.7333333333333329</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="W2" t="n">
-        <v>-7.666666666666666</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.7333333333333329</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>71.22727272727272</v>
       </c>
       <c r="AM2" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
+      <c r="AN2" t="n">
         <v>-5.786111111111126</v>
       </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
+        <v>-0.6529583972743467</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-5.53524554758107</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-20828499.91459402</v>
+      </c>
+      <c r="AS2" t="n">
         <v>-29846130.95238096</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AT2" t="n">
+        <v>-0.2652031356801094</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.6529761904761904</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>-2.036111111111097</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.610714285714284</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
         <v>-6.928968253968279</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>-0.6529583972743467</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-0.6529761904761904</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.610714285714284</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>1.697725122744469</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-2.036111111111097</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.2652031356801094</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="n">
         <v>-4.617364768874054</v>
       </c>
-      <c r="BE2" t="n">
-        <v>-5.53524554758107</v>
-      </c>
       <c r="BF2" t="n">
-        <v>-20828499.91459402</v>
+        <v>1.697725122744469</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -984,103 +984,103 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.416666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="V3" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="Z3" t="n">
         <v>6.75</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>10</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="AD3" t="n">
         <v>0.5366666666666666</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AE3" t="n">
         <v>0.8383333333333336</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-4.333333333333336</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.333333333333336</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.416666666666666</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AK3" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AF3" t="n">
-        <v>2.083333333333334</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
         <v>78.76801346801348</v>
       </c>
       <c r="AM3" t="n">
         <v>77.85375573921029</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>-7.186501377410465</v>
-      </c>
+      <c r="AN3" t="n">
+        <v>-7.368484848484854</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-51413177.2268136</v>
+        <v>4.663911373155372</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.217263544536266</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+        <v>-3.922110422454423</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-30861818.17709465</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-52528383.83838384</v>
+      </c>
       <c r="AT3" t="n">
-        <v>4.662498772541994</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-1.347658402203856</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-3.051790633608814</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>-0.6644494615050729</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-1.394848484848485</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>0.7455555555555406</v>
+      </c>
       <c r="AY3" t="n">
-        <v>-1.691146771888398</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.020018365472879</v>
-      </c>
+        <v>-3.228484848484843</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-0.6495899142606152</v>
+        <v>-4.290404040404042</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-6.978295722220025</v>
-      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>-3.821670648389343</v>
+        <v>-7.193227926985998</v>
       </c>
       <c r="BF3" t="n">
-        <v>-30582204.89040975</v>
+        <v>-1.702080137329435</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1165,103 +1165,103 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-5</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>2</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
         <v>-0.8949999999999998</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
         <v>1.085</v>
       </c>
-      <c r="Z4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AK4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
         <v>77.95454545454545</v>
       </c>
       <c r="AM4" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>-0.02499999999999147</v>
-      </c>
+      <c r="AN4" t="n">
+        <v>0.08279220779220964</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-2840227.272727277</v>
+        <v>-3.019159858832978</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.015909090909076</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+        <v>1.164141144634812</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-780645.2390500437</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-2588798.701298706</v>
+      </c>
       <c r="AT4" t="n">
-        <v>-3.412103922423285</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>-0.2500000000000004</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.4215909090909093</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>-0.07075274904011941</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.2418831168831173</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>0.7142857142857224</v>
+      </c>
       <c r="AY4" t="n">
-        <v>-1.758528781459191</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.8818181818181756</v>
-      </c>
+        <v>0.4009740259740262</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-0.0591532846929772</v>
+        <v>-0.9415584415584277</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>0.5584070336754223</v>
-      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>1.213244601807162</v>
+        <v>0.4662913277439316</v>
       </c>
       <c r="BF4" t="n">
-        <v>-373016.4704373358</v>
+        <v>-1.6851765897053</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1346,103 +1346,103 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V5" t="n">
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
         <v>12.5</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>1</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.9299999999999998</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
         <v>-1.285</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>-4</v>
       </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AJ5" t="n">
         <v>2</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AF5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
         <v>77.62272727272727</v>
       </c>
       <c r="AM5" t="n">
         <v>76.5</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-0.5788961038960849</v>
-      </c>
+      <c r="AN5" t="n">
+        <v>-1.028571428571425</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-6566688.311688308</v>
+        <v>-2.482223040731469</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.115584415584408</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+        <v>-1.855779584561105</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-4560738.276371153</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-7768311.688311685</v>
+      </c>
       <c r="AT5" t="n">
-        <v>-2.344286824578319</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>0.03051948051948061</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.751623376623378</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>0.03935195290237292</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.02467532467532463</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>0.7597402597402549</v>
+      </c>
       <c r="AY5" t="n">
-        <v>3.723382610620007</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.532467532467507</v>
-      </c>
+        <v>1.584415584415584</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>0.01246849118435223</v>
+        <v>-1.303896103896093</v>
       </c>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>-0.1528413069773364</v>
-      </c>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>-1.910130074757177</v>
+        <v>-0.06373503947033043</v>
       </c>
       <c r="BF5" t="n">
-        <v>-5104078.211303459</v>
+        <v>3.697361368789938</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,103 +1527,103 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.666666666666667</v>
+        <v>-3.166666666666667</v>
       </c>
       <c r="V6" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="Z6" t="n">
         <v>22.66666666666667</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
         <v>-21.66666666666667</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AD6" t="n">
         <v>2.831666666666667</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
         <v>-2.891666666666667</v>
       </c>
-      <c r="Z6" t="n">
-        <v>18.33333333333334</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-18.33333333333334</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>3</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AK6" t="n">
         <v>-3</v>
       </c>
-      <c r="AF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-11.33333333333333</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-3.166666666666667</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
         <v>75.97205387205388</v>
       </c>
       <c r="AM6" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>6.823302469135797</v>
-      </c>
+      <c r="AN6" t="n">
+        <v>7.060763888888886</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>45962553.04783951</v>
+        <v>-1.492309818664296</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.690779320987659</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+        <v>5.901018756784993</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>28947364.23277445</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>47881727.43055556</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-1.181552868356249</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>0.7966820987654317</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-1.871527777777775</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+        <v>0.4727499731950198</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.8263888888888886</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>0.07986111111111427</v>
+      </c>
       <c r="AY6" t="n">
-        <v>0.359199190042844</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.1163194444444287</v>
-      </c>
+        <v>-1.880208333333332</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>0.4806652884439262</v>
+        <v>6.868055555555557</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>9.138795685738401</v>
-      </c>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
-        <v>5.931281691304903</v>
+        <v>9.096245041078632</v>
       </c>
       <c r="BF6" t="n">
-        <v>29274081.18949334</v>
+        <v>0.3440181335692181</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1632,7 +1632,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,22 +1684,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>-2</v>
@@ -1708,103 +1708,103 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="Y7" t="n">
         <v>-0.25</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.4700000000000002</v>
-      </c>
       <c r="Z7" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="AB7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK7" t="n">
         <v>-2</v>
       </c>
-      <c r="AC7" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>81.76666666666667</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AM7" t="n">
-        <v>80.13415404040404</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>-0.03749999999999432</v>
-      </c>
+        <v>75.80000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.171753246753255</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>-112321.4285714291</v>
+        <v>8.326102350265018</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.2910714285714278</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+        <v>-3.315135535049265</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1432068.723799587</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1775953.282828284</v>
+      </c>
       <c r="AT7" t="n">
-        <v>2.362852243863756</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>0.1089285714285715</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.9857142857142875</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+        <v>-0.06534905438147809</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.2233766233766232</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>1.620490620490642</v>
+      </c>
       <c r="AY7" t="n">
-        <v>0.9000830395087078</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.742857142857105</v>
-      </c>
+        <v>1.663816738816742</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>0.1161873589842288</v>
+        <v>-0.9375901875902031</v>
       </c>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>0.9510967786844304</v>
-      </c>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="n">
-        <v>0.3619543532862792</v>
+        <v>-0.2109521425847163</v>
       </c>
       <c r="BF7" t="n">
-        <v>-238945.7190112025</v>
+        <v>1.618717119284788</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1821,24 +1821,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,127 +1865,127 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13</v>
+      </c>
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-2</v>
-      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.25</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.25</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W8" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.24</v>
+        <v>-1.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.1925</v>
+        <v>-2.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>-14.75</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>14.75</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3.75</v>
+        <v>-2.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.25</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>1.316</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-2.75</v>
-      </c>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
       <c r="AL8" t="n">
-        <v>77.02146464646464</v>
+        <v>73.29545454545455</v>
       </c>
       <c r="AM8" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>1.214520202020211</v>
-      </c>
+        <v>72.99111111111111</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.902169421487613</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>1834589.646464648</v>
+        <v>2.517704458265484</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.000631313131322</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+        <v>2.96223784474266</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10053627.24598238</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>14692283.05785124</v>
+      </c>
       <c r="AT8" t="n">
-        <v>8.367477054386455</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>0.213762626262626</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.680429292929293</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+        <v>0.4238095238095236</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.5102272727272728</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>5.375206611570235</v>
+      </c>
       <c r="AY8" t="n">
-        <v>1.436444162587492</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.566919191919197</v>
-      </c>
+        <v>0.7660123966942081</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>-0.04747189620826719</v>
+        <v>4.699896694214871</v>
       </c>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>-0.2379628116184165</v>
-      </c>
+      <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="n">
-        <v>-3.104791532682242</v>
+        <v>3.202640962511481</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1201358.571683187</v>
+        <v>1.409744653790366</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2002,24 +2002,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2046,127 +2046,127 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>-2</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.8</v>
+        <v>0.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="V9" t="n">
-        <v>7.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>1.316</v>
+        <v>-2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3799999999999999</v>
+        <v>-2.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.5</v>
+        <v>-6</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.800000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6000000000000001</v>
+        <v>-0.0349999999999997</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.2999999999999998</v>
-      </c>
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>2.2</v>
+        <v>-1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AL9" t="n">
-        <v>73.29545454545455</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AM9" t="n">
-        <v>72.99111111111111</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>4.902169421487613</v>
-      </c>
+        <v>80.13415404040404</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.03749999999999432</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>14692283.05785124</v>
+        <v>2.362852243863756</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.699896694214871</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>0.3619543532862792</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-238945.7190112025</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-112321.4285714291</v>
+      </c>
       <c r="AT9" t="n">
-        <v>2.517704458265484</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>0.5102272727272728</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.7660123966942081</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+        <v>0.1161873589842288</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.1089285714285715</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>3.742857142857105</v>
+      </c>
       <c r="AY9" t="n">
-        <v>1.409744653790366</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.375206611570235</v>
-      </c>
+        <v>0.9857142857142875</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>0.4238095238095236</v>
+        <v>-0.2910714285714278</v>
       </c>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>3.202640962511481</v>
-      </c>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
-        <v>2.96223784474266</v>
+        <v>0.9510967786844304</v>
       </c>
       <c r="BF9" t="n">
-        <v>10053627.24598238</v>
+        <v>0.9000830395087078</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2247,101 +2247,101 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AB10" t="n">
         <v>0.25</v>
       </c>
-      <c r="U10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
         <v>-0.1925000000000001</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="n">
         <v>-1.3675</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AI10" t="n">
         <v>-4</v>
       </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AJ10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AK10" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AF10" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
+      <c r="AN10" t="n">
         <v>-12.20606060606062</v>
       </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
+        <v>-0.06185875316307943</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-11.21757821486082</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-32647976.76558546</v>
+      </c>
+      <c r="AS10" t="n">
         <v>-45110909.09090909</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AT10" t="n">
+        <v>-0.8513400046008743</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-1.65050505050505</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-0.6909090909090878</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.4595959595959549</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
         <v>-11.28787878787877</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>-0.06185875316307943</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>-1.65050505050505</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.4595959595959549</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="n">
-        <v>1.938006096158269</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-0.6909090909090878</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-0.8513400046008743</v>
       </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="n">
         <v>-10.60447435012652</v>
       </c>
-      <c r="BE10" t="n">
-        <v>-11.21757821486082</v>
-      </c>
       <c r="BF10" t="n">
-        <v>-32647976.76558546</v>
+        <v>1.938006096158269</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2426,103 +2426,103 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.8125</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AE11" t="n">
         <v>-0.08499999999999996</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>-0.3999999999999999</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AK11" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>77.97987603305785</v>
+        <v>78.01627272727274</v>
       </c>
       <c r="AM11" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
+      <c r="AN11" t="n">
         <v>2.722746950019683</v>
       </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
+        <v>2.544944017851492</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.024274162893079</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10984469.04336654</v>
+      </c>
+      <c r="AS11" t="n">
         <v>17019983.60225633</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AT11" t="n">
+        <v>0.5276486675638035</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.6762691853600942</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>0.7954742227468898</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-2.333989243080151</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
         <v>5.466745375836283</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="n">
-        <v>2.544944017851492</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>0.6762691853600942</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-2.333989243080151</v>
-      </c>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="n">
-        <v>-3.654831907610326</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.7954742227468898</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.5276486675638035</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="n">
         <v>0.02235611336402599</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.024274162893079</v>
-      </c>
       <c r="BF11" t="n">
-        <v>10984469.04336654</v>
+        <v>-3.654831907610326</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2607,103 +2607,103 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AC12" t="n">
         <v>4</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-7.333333333333333</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AD12" t="n">
         <v>-0.3266666666666667</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
         <v>-1.066666666666667</v>
       </c>
-      <c r="Z12" t="n">
-        <v>5.666666666666664</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-5.666666666666664</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>-2</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AK12" t="n">
         <v>2</v>
       </c>
-      <c r="AF12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
         <v>72.98888888888888</v>
       </c>
       <c r="AM12" t="n">
         <v>69</v>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="n">
+      <c r="AN12" t="n">
         <v>4.648877665544319</v>
       </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="n">
+        <v>0.8657106619825754</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.016572387689507</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3577584.255148304</v>
+      </c>
+      <c r="AS12" t="n">
         <v>6137873.176206509</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AT12" t="n">
+        <v>0.04603727455894635</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.1550505050505051</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>2.392087542087609</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.061503928170595</v>
+      </c>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
         <v>4.746520763187448</v>
-      </c>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="n">
-        <v>0.8657106619825754</v>
-      </c>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>0.1550505050505051</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-1.061503928170595</v>
-      </c>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="n">
-        <v>2.571972157433972</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.392087542087609</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.04603727455894635</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="n">
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="n">
         <v>7.331146766698879</v>
       </c>
-      <c r="BE12" t="n">
-        <v>3.016572387689507</v>
-      </c>
       <c r="BF12" t="n">
-        <v>3577584.255148304</v>
+        <v>2.571972157433972</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2712,27 +2712,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2762,55 +2767,125 @@
           <t>8tPSZqtA</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.665</v>
+      </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
       <c r="AL13" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>69.5409090909091</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.123376623376615</v>
+      </c>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>-4.192364047068082</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.433221114532756</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1651013.664523781</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1776341.991341992</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.01481295416717421</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.09220779220779241</v>
+      </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-3.160173160173173</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-2.962770562770565</v>
+      </c>
       <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>4.493073593073603</v>
+      </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+      <c r="BE13" t="n">
+        <v>4.043052003410054</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.0640253202730392</v>
+      </c>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -2818,32 +2893,27 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2873,125 +2943,55 @@
           <t>8tPSZqtA</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>8</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>71.18181818181819</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>69.5409090909091</v>
-      </c>
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="n">
-        <v>2.123376623376615</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1776341.991341992</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4.493073593073603</v>
-      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="n">
-        <v>-4.192364047068082</v>
-      </c>
+      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="n">
-        <v>0.09220779220779241</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-2.962770562770565</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="n">
-        <v>0.0640253202730392</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-3.160173160173173</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.01481295416717421</v>
-      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="n">
-        <v>4.043052003410054</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.433221114532756</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1651013.664523781</v>
-      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3105,32 +3105,27 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3155,12 +3150,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>-2</v>
       </c>
@@ -3190,10 +3185,10 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AL16" t="n">
+        <v>69.13636363636363</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
@@ -3220,7 +3215,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3229,18 +3224,18 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3267,16 +3262,16 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
@@ -3301,7 +3296,7 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>69.13636363636363</v>
+        <v>69.2</v>
       </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -3330,27 +3325,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3375,54 +3375,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.73</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3376984126984013</v>
+      </c>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>0.2953982603720817</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.5411850373547225</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-130365.5393059938</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-1281253.306878306</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>1.906944444444434</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4.621296296296293</v>
+      </c>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>-5.914153439153438</v>
+      </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BE18" t="n">
+        <v>0.4217652273900256</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.216519796764572</v>
+      </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
@@ -3430,27 +3506,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3476,10 +3557,18 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-2</v>
+      </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>-1</v>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
         <v>0</v>
@@ -3503,7 +3592,9 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
@@ -3634,7 +3725,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3643,18 +3734,18 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3679,19 +3770,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>0</v>
@@ -3714,9 +3797,7 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="n">
-        <v>69.2</v>
-      </c>
+      <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
@@ -3744,7 +3825,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -3753,18 +3834,18 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3789,24 +3870,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-1</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>0</v>
       </c>
@@ -3828,9 +3897,7 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
@@ -3858,7 +3925,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -3867,18 +3934,18 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">dw stadium
+  wigan </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3905,9 +3972,13 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
         <v>0</v>
@@ -3958,7 +4029,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -3967,18 +4038,18 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4005,18 +4076,22 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1</v>
+      </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -4039,7 +4114,7 @@
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="n">
-        <v>70.70833333333333</v>
+        <v>69.64141414141415</v>
       </c>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -4068,7 +4143,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -4077,18 +4152,18 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4168,7 +4243,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4177,18 +4252,18 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4216,12 +4291,12 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
         <v>0</v>
@@ -4272,7 +4347,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -4281,18 +4356,18 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4372,7 +4447,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -4381,18 +4456,18 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4419,12 +4494,8 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
@@ -4476,32 +4547,27 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4528,128 +4594,62 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>0</v>
       </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>9</v>
-      </c>
-      <c r="X29" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>74</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>69</v>
-      </c>
+        <v>70.70833333333333</v>
+      </c>
+      <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="n">
-        <v>0.3376984126984013</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-1281253.306878306</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>-5.914153439153438</v>
-      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="n">
-        <v>0.2953982603720817</v>
-      </c>
+      <c r="AT29" t="inlineStr"/>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.621296296296293</v>
-      </c>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="n">
-        <v>1.216519796764572</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.906944444444434</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="n">
-        <v>0.4217652273900256</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>-0.5411850373547225</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>-130365.5393059938</v>
-      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
       <c r="BG29" t="n">
         <v>0</v>
       </c>
@@ -4657,7 +4657,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -4666,18 +4666,18 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4757,27 +4757,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4803,7 +4808,11 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -4830,7 +4839,9 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>72.22962962962963</v>
+      </c>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
@@ -4857,7 +4868,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -4866,18 +4877,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4957,27 +4968,32 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5002,54 +5018,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>21</v>
+      </c>
+      <c r="W33" t="n">
+        <v>-21</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
+      <c r="AH33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-2.816666666666649</v>
+      </c>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
+      <c r="AP33" t="n">
+        <v>-0.2023692810457476</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>-2.49301163447835</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>-1269591.292981506</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>-2234641.203703703</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
       <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AX33" t="n">
+        <v>-1.420370370370335</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>-0.5010416666666657</v>
+      </c>
       <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+      <c r="BA33" t="n">
+        <v>-2.82534722222222</v>
+      </c>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
-      <c r="BF33" t="inlineStr"/>
+      <c r="BE33" t="n">
+        <v>-2.202103660443441</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.301905073233439</v>
+      </c>
       <c r="BG33" t="n">
         <v>0</v>
       </c>
@@ -5157,7 +5249,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5166,18 +5258,18 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5202,11 +5294,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -5233,9 +5321,7 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="n">
-        <v>69.33522727272728</v>
-      </c>
+      <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
@@ -5263,32 +5349,27 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5315,128 +5396,58 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
         <v>0</v>
       </c>
-      <c r="T36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>7</v>
-      </c>
-      <c r="W36" t="n">
-        <v>-24</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>70.18181818181819</v>
-      </c>
+        <v>71.47727272727272</v>
+      </c>
+      <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="n">
-        <v>-2.816666666666649</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>-2234641.203703703</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>-2.82534722222222</v>
-      </c>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="n">
-        <v>-0.2023692810457476</v>
-      </c>
+      <c r="AT36" t="inlineStr"/>
       <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>-0.5010416666666657</v>
-      </c>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="n">
-        <v>1.301905073233439</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>-1.420370370370335</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="n">
-        <v>-2.202103660443441</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>-2.49301163447835</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>-1269591.292981506</v>
-      </c>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
       <c r="BG36" t="n">
         <v>0</v>
       </c>
@@ -5444,32 +5455,27 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5495,11 +5501,7 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -5526,9 +5528,7 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr"/>
@@ -5670,7 +5670,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5679,18 +5679,18 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5717,13 +5717,9 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>0</v>
@@ -5774,7 +5770,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -5783,18 +5779,18 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5819,11 +5815,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -5850,9 +5842,7 @@
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
@@ -5880,32 +5870,27 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5931,14 +5916,14 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>-2</v>
+      </c>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>-1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
         <v>0</v>
@@ -5962,9 +5947,7 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="n">
-        <v>71.77777777777777</v>
-      </c>
+      <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="inlineStr"/>
@@ -5991,7 +5974,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6000,18 +5983,18 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6036,7 +6019,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
@@ -6063,7 +6050,9 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
+      <c r="AL42" t="n">
+        <v>69.33522727272728</v>
+      </c>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
@@ -6091,27 +6080,32 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6137,7 +6131,11 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -6164,7 +6162,9 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
+      <c r="AM43" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
@@ -6589,103 +6589,103 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>7</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
         <v>0.75</v>
       </c>
-      <c r="V47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X47" t="n">
+      <c r="AD47" t="n">
         <v>0.1174999999999999</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AE47" t="n">
         <v>0.5950000000000002</v>
       </c>
-      <c r="Z47" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>-1.25</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AK47" t="n">
         <v>1</v>
       </c>
-      <c r="AF47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
         <v>76.15625</v>
       </c>
       <c r="AM47" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="n">
-        <v>-5.467217630854009</v>
-      </c>
+      <c r="AN47" t="n">
+        <v>-5.649201101928398</v>
+      </c>
+      <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="n">
-        <v>-42477277.31864096</v>
+        <v>5.572761884128397</v>
       </c>
       <c r="AQ47" t="n">
-        <v>-3.063360881542692</v>
-      </c>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
+        <v>-3.786451794156378</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>-27821847.68622385</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>-43592483.9302112</v>
+      </c>
       <c r="AT47" t="n">
-        <v>5.571349283515019</v>
-      </c>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="n">
-        <v>-0.8917355371900828</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>-1.708723599632687</v>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+        <v>-0.4920997390452169</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>-0.9389256198347109</v>
+      </c>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="n">
+        <v>2.633526170798888</v>
+      </c>
       <c r="AY47" t="n">
-        <v>-0.6278392923824185</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>2.907988980716226</v>
-      </c>
+        <v>-1.885417814508717</v>
+      </c>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
-        <v>-0.4772401918007592</v>
+        <v>-3.136501377410468</v>
       </c>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="n">
-        <v>-5.534005271769757</v>
-      </c>
+      <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="n">
-        <v>-3.686012020091297</v>
+        <v>-5.74893747653573</v>
       </c>
       <c r="BF47" t="n">
-        <v>-27542234.39953895</v>
+        <v>-0.6387726578234556</v>
       </c>
       <c r="BG47" t="n">
         <v>1</v>
